--- a/foro_app/documentation/precificacao_foro_semanal.xlsx
+++ b/foro_app/documentation/precificacao_foro_semanal.xlsx
@@ -585,13 +585,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>97</v>
+        <v>129.9</v>
       </c>
       <c r="D2" t="n">
-        <v>197</v>
+        <v>199.9</v>
       </c>
       <c r="E2" t="n">
-        <v>397</v>
+        <v>399.9</v>
       </c>
     </row>
     <row r="3">
@@ -639,13 +639,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>20</v>
